--- a/PreWeek2/homework1.xlsx
+++ b/PreWeek2/homework1.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jadacarter\Documents\DataAnalytics\PreWeek2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{005B970B-6A4C-43E2-9FCA-380E8A7F0628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFA96B44-08D6-4A08-A3C7-B8E3142F5A67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17280" windowHeight="9960" xr2:uid="{1B0AFC83-732B-4610-B835-4EEEC5A5D10F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="1" xr2:uid="{1B0AFC83-732B-4610-B835-4EEEC5A5D10F}"/>
   </bookViews>
   <sheets>
     <sheet name="Store_Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Store_Summary" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Store</t>
   </si>
@@ -62,17 +63,23 @@
     <t>MEAN</t>
   </si>
   <si>
-    <t>STANDARD WITH DEVIATION STORE H</t>
-  </si>
-  <si>
     <t>WITHOUT STORE H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STANDARD  DEVIATION </t>
+  </si>
+  <si>
+    <t>Store Sales Summary</t>
+  </si>
+  <si>
+    <t>The overall average monthly sales performance is approximately 49.42, which indicates that most stores sell around 49 to 50 units per month. The sales figures are generally fairly consistent, with most stores falling between 43 and 52. The standard deviation of 7.63 suggests some variation in performance across locations. However, one store, Store H, reported sales of 72, which is much higher than the rest of the stores. When Store H is removed from the calculation, the standard deviation decreases significantly, showing that this value has a strong influence on the results. This suggests that store performance is more tightly grouped than it first appears. To better understand the differences in performance, I would want additional information such as store size, location, customer traffic, and promotional activities.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -84,6 +91,19 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -109,13 +129,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -132,6 +158,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -482,7 +512,7 @@
         <v>49.416666666666664</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H2">
         <f>_xlfn.STDEV.S(B2:B13)</f>
@@ -505,7 +535,7 @@
         <v>47.5</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H3">
         <f>_xlfn.STDEV.S(B2:B8,B10:B13)</f>
@@ -620,4 +650,99 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95BF27BB-41F0-483D-900E-D7CF75F7872A}">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="6" width="15.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+    </row>
+    <row r="2" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:F10"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>